--- a/e_pod_line_simulator/configs/产线配置模板.xlsx
+++ b/e_pod_line_simulator/configs/产线配置模板.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工序" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="产线配置" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原料" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="到货计划" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +472,46 @@
           <t>缓冲区容量</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>机台节拍(秒)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>清洗时间(分钟)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>抽检比例</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>缺陷率</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>返工时长(分钟)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>工种</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>洁净区</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>BOM(组件:用量;...)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +542,26 @@
       <c r="H2" t="n">
         <v>100</v>
       </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>通用装配工</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -529,6 +592,26 @@
       <c r="H3" t="n">
         <v>100</v>
       </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>通用装配工</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,6 +642,26 @@
       <c r="H4" t="n">
         <v>100</v>
       </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>通用装配工</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -588,6 +691,220 @@
       </c>
       <c r="H5" t="n">
         <v>100</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>通用装配工</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>配置项</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>production_type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>assembly</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>shift_hours</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>break_minutes</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>worker_hourly_wage</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cip_interval_batches</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cip_interval_hours</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>changeover_matrix_json</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>原料名</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>初始库存</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>棉芯</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>到货时间(分钟)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>原料</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>棉芯</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
